--- a/output/2026-09-03_18_Italia_Basilicata_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-03_18_Italia_Basilicata_Depolverazione_Trattamento_aria.xlsx
@@ -498,10 +498,9 @@
           <t>0835 264263 / 392 9823056</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda confermata attiva da oltre 30 anni nella vendita di macchine e attrezzature per pulizia industriale, tra cui aspiraliquidi, aspiratori industriali, compressori, generatori aria calda, idropulitrici, spazzatrici. Sede: Contrada Serra Paducci, Zona Commerciale 2, 75100 Matera (MT). Distribuzione estesa a Puglia e Basilicata. Email generica non reperita.</t>
+          <t>Azienda confermata attiva da oltre 30 anni nella vendita di macchine e attrezzature per pulizia industriale, tra cui aspiraliquidi, aspiratori industriali, compressori, generatori aria calda, idropulitrici, spazzatrici. Sede: Contrada Serra Paducci, Zona Commerciale 2, 75100 Matera (MT). Distribuzione estesa a Puglia e Basilicata. Email generica non reperita. [DUPLICATO — vedi anche: 2026-09-03_17_Italia_Basilicata_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +542,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda confermata, attiva da 25 anni nella vendita di macchine e attrezzature per pulizia industriale (aspiratori, idropulitrici, lavapavimenti, spazzatrici, lavamoquette). Operativa a Matera e in Basilicata/Puglia. Indirizzo esatto non reperito nelle fonti consultate (solo 'Matera, MT').</t>
+          <t>Azienda confermata, attiva da 25 anni nella vendita di macchine e attrezzature per pulizia industriale (aspiratori, idropulitrici, lavapavimenti, spazzatrici, lavamoquette). Operativa a Matera e in Basilicata/Puglia. Indirizzo esatto non reperito nelle fonti consultate (solo 'Matera, MT'). [DUPLICATO — vedi anche: 2026-09-03_17_Italia_Basilicata_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
